--- a/GANsEvaluation.xlsx
+++ b/GANsEvaluation.xlsx
@@ -537,22 +537,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100.892</v>
+        <v>96.447</v>
       </c>
       <c r="D4" t="n">
-        <v>6.534</v>
+        <v>6.512</v>
       </c>
       <c r="E4" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
       <c r="F4" t="n">
-        <v>87.247</v>
+        <v>87.348</v>
       </c>
       <c r="G4" t="n">
-        <v>6.091</v>
+        <v>6.072</v>
       </c>
       <c r="H4" t="n">
-        <v>0.406</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="5">
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>176.236</v>
+        <v>178.706</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>7.052</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.593</v>
+        <v>7.038</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.708</v>
       </c>
       <c r="F5" t="n">
-        <v>129.69</v>
+        <v>127.276</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6.537</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0.762</v>
+        <v>6.552</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5580000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -593,22 +593,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>203.238</v>
+        <v>206.091</v>
       </c>
       <c r="D6" t="n">
-        <v>6.203</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0.651</v>
+        <v>6.371</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.58</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>204.093</v>
+        <v>203.843</v>
       </c>
       <c r="G6" t="n">
-        <v>5.538</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.652</v>
+        <v>5.761</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.666</v>
       </c>
     </row>
     <row r="7">
@@ -621,22 +621,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>98.88800000000001</v>
+        <v>98.313</v>
       </c>
       <c r="D7" t="n">
-        <v>6.868</v>
+        <v>6.801</v>
       </c>
       <c r="E7" t="n">
-        <v>0.569</v>
+        <v>0.4</v>
       </c>
       <c r="F7" t="n">
-        <v>88.452</v>
+        <v>89.562</v>
       </c>
       <c r="G7" t="n">
-        <v>6.297</v>
+        <v>6.191</v>
       </c>
       <c r="H7" t="n">
-        <v>0.249</v>
+        <v>0.287</v>
       </c>
     </row>
   </sheetData>
